--- a/exemplos_para_envio/COM ERRO - B2 Candoi 09-2026.xlsx
+++ b/exemplos_para_envio/COM ERRO - B2 Candoi 09-2026.xlsx
@@ -13,9 +13,9 @@
     <sheet name="DESPESAS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2979,13 +2979,13 @@
         <v>28663</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>7097</v>
       </c>
       <c r="F93" s="12" t="n">
-        <v>36556</v>
+        <v>61556</v>
       </c>
       <c r="G93" s="13" t="n">
         <v>6.783</v>
@@ -3007,13 +3007,13 @@
         <v>0</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>3632</v>
+        <v>3357</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>27850</v>
+        <v>28123</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>6.48</v>
+        <v>6.484</v>
       </c>
     </row>
     <row r="95">
@@ -3032,13 +3032,13 @@
         <v>0</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>998</v>
+        <v>898</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>7933</v>
+        <v>8034</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>6.88</v>
+        <v>6.886</v>
       </c>
     </row>
     <row r="96">
@@ -3057,13 +3057,13 @@
         <v>0</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>1042</v>
+        <v>1032</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>7813</v>
+        <v>7822</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>4.69</v>
+        <v>4.686</v>
       </c>
     </row>
     <row r="97">
@@ -3076,19 +3076,19 @@
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>36556</v>
+        <v>61556</v>
       </c>
       <c r="D97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E97" s="12" t="n">
-        <v>7774</v>
+        <v>7202</v>
       </c>
       <c r="F97" s="12" t="n">
-        <v>28762</v>
+        <v>54349</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>6.778</v>
+        <v>6.781</v>
       </c>
     </row>
     <row r="98">
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>27850</v>
+        <v>28123</v>
       </c>
       <c r="D98" s="9" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         <v>4496</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>23351</v>
+        <v>23624</v>
       </c>
       <c r="G98" s="10" t="n">
         <v>6.483</v>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>7933</v>
+        <v>8034</v>
       </c>
       <c r="D99" s="12" t="n">
         <v>0</v>
@@ -3135,10 +3135,10 @@
         <v>1162</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>6769</v>
+        <v>6870</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>6.879</v>
+        <v>6.887</v>
       </c>
     </row>
     <row r="100">
@@ -3151,7 +3151,7 @@
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>7813</v>
+        <v>7822</v>
       </c>
       <c r="D100" s="9" t="n">
         <v>0</v>
@@ -3160,10 +3160,10 @@
         <v>1284</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>6528</v>
+        <v>6536</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>4.686</v>
+        <v>4.685</v>
       </c>
     </row>
     <row r="101">
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>28762</v>
+        <v>54349</v>
       </c>
       <c r="D101" s="12" t="n">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>8265</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>20495</v>
+        <v>46082</v>
       </c>
       <c r="G101" s="13" t="n">
         <v>6.783</v>
@@ -3201,19 +3201,19 @@
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>23351</v>
+        <v>23624</v>
       </c>
       <c r="D102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>3940</v>
+        <v>4098</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>19403</v>
+        <v>19514</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>6.486</v>
+        <v>6.479</v>
       </c>
     </row>
     <row r="103">
@@ -3226,19 +3226,19 @@
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>6769</v>
+        <v>6870</v>
       </c>
       <c r="D103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E103" s="12" t="n">
-        <v>1113</v>
+        <v>1041</v>
       </c>
       <c r="F103" s="12" t="n">
-        <v>5656</v>
+        <v>5827</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>6.881</v>
+        <v>6.882</v>
       </c>
     </row>
     <row r="104">
@@ -3251,19 +3251,19 @@
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>6528</v>
+        <v>6536</v>
       </c>
       <c r="D104" s="9" t="n">
         <v>5000</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>1181</v>
+        <v>1141</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>10345</v>
+        <v>10394</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>4.685</v>
+        <v>4.681</v>
       </c>
     </row>
     <row r="105">
@@ -3276,19 +3276,19 @@
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>20495</v>
+        <v>46082</v>
       </c>
       <c r="D105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>8653</v>
+        <v>8214</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>11829</v>
+        <v>37866</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>6.783</v>
+        <v>6.784</v>
       </c>
     </row>
     <row r="106">
@@ -3301,19 +3301,19 @@
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>19403</v>
+        <v>19514</v>
       </c>
       <c r="D106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>2529</v>
+        <v>2852</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>16872</v>
+        <v>16660</v>
       </c>
       <c r="G106" s="10" t="n">
-        <v>6.484</v>
+        <v>6.479</v>
       </c>
     </row>
     <row r="107">
@@ -3326,19 +3326,19 @@
         </is>
       </c>
       <c r="C107" s="12" t="n">
-        <v>5656</v>
+        <v>5827</v>
       </c>
       <c r="D107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>589</v>
+        <v>732</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>5066</v>
+        <v>5095</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>6.887</v>
+        <v>6.883</v>
       </c>
     </row>
     <row r="108">
@@ -3351,19 +3351,19 @@
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>10345</v>
+        <v>10394</v>
       </c>
       <c r="D108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>695</v>
+        <v>756</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>9649</v>
+        <v>9636</v>
       </c>
       <c r="G108" s="10" t="n">
-        <v>4.681</v>
+        <v>4.686</v>
       </c>
     </row>
     <row r="109">
@@ -3376,23 +3376,323 @@
         </is>
       </c>
       <c r="C109" s="12" t="n">
-        <v>11829</v>
+        <v>37866</v>
       </c>
       <c r="D109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E109" s="12" t="n">
-        <v>5196</v>
+        <v>5990</v>
       </c>
       <c r="F109" s="12" t="n">
-        <v>6617</v>
+        <v>31867</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>6.786</v>
+        <v>6.781</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>16660</v>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>3489</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>38166</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>6.486</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>5095</v>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>1063</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>9029</v>
+      </c>
+      <c r="G111" s="13" t="n">
+        <v>6.879</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>9636</v>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>1113</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>8523</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>4.679</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="n">
+        <v>31867</v>
+      </c>
+      <c r="D113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>7823</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>24029</v>
+      </c>
+      <c r="G113" s="13" t="n">
+        <v>6.783</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>38166</v>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>3909</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>34249</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>6.479</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="n">
+        <v>9029</v>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>1041</v>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>7987</v>
+      </c>
+      <c r="G115" s="13" t="n">
+        <v>6.883</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>8523</v>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>968</v>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>7555</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>4.682</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>24029</v>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>7982</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>16037</v>
+      </c>
+      <c r="G117" s="13" t="n">
+        <v>6.784</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>34249</v>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="9" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>29865</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>6.479</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="n">
+        <v>7987</v>
+      </c>
+      <c r="D119" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v>1087</v>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>6899</v>
+      </c>
+      <c r="G119" s="13" t="n">
+        <v>6.881</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>7555</v>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>1140</v>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>6412</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>4.683</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="n">
+        <v>16037</v>
+      </c>
+      <c r="D121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>8710</v>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>7315</v>
+      </c>
+      <c r="G121" s="13" t="n">
+        <v>6.785</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H109"/>
+  <autoFilter ref="A1:H121"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -3408,7 +3708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3926,13 +4226,13 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>6.1235</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>91852.13</v>
+        <v>244939.02</v>
       </c>
       <c r="F19" t="n">
         <v>158447</v>
@@ -3956,22 +4256,76 @@
         <v>5000</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>3.986</v>
+        <v>4.011</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>19929.79</v>
+        <v>20054.79</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>158481</v>
+        <v>158453</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Distribuidora Paraná</t>
+          <t>Distribuidora Sul</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>5.7556</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>143890.65</v>
+      </c>
+      <c r="F21" t="n">
+        <v>158471</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Distribuidora Alfa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>5.9036</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>29517.89</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>158478</v>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Distribuidora Alfa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G22"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -3987,7 +4341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4020,56 +4374,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="15" t="n">
-        <v>1870.31</v>
+        <v>57707.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>57922.43</v>
+        <v>3402.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Coleta de resíduos (óleo e borra)</t>
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>3309.6</v>
+        <v>1227.94</v>
       </c>
     </row>
     <row r="5">
@@ -4092,38 +4446,38 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>824.61</v>
+        <v>1028.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>1373.09</v>
+        <v>1036.1</v>
       </c>
     </row>
     <row r="8">
@@ -4132,34 +4486,34 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>1196.05</v>
+        <v>4209.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Reparo elétrico</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>3965.92</v>
+        <v>2505.28</v>
       </c>
     </row>
     <row r="10">
@@ -4177,7 +4531,7 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>8001.05</v>
+        <v>7895.53</v>
       </c>
     </row>
     <row r="11">
@@ -4195,25 +4549,25 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1076.02</v>
+        <v>905.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46285</v>
+        <v>46281</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>20027.08</v>
+        <v>1493.02</v>
       </c>
     </row>
     <row r="13">
@@ -4222,52 +4576,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>4002.17</v>
+        <v>20601.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D14" s="15" t="n">
-        <v>1328.43</v>
+        <v>1834.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
-        <v>46290</v>
+        <v>46285</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fretes</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frete das entregas de combustível</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>6820</v>
+        <v>4094.73</v>
       </c>
     </row>
     <row r="16">
@@ -4276,16 +4630,16 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Fretes</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Frete das entregas de combustível</t>
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>1861.4</v>
+        <v>8030</v>
       </c>
     </row>
     <row r="17">
@@ -4303,11 +4657,29 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>4015.39</v>
+        <v>3778.64</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Taxas de cartão</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Taxas das maquininhas (semana)</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>1783.75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D17"/>
+  <autoFilter ref="A1:D18"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Folha de pagamento,Aluguel,Energia elétrica,Água e esgoto,Taxas de cartão,Manutenção,Fretes,Sistemas e contabilidade,Marketing,Outras despesas"</formula1>
